--- a/data/AR_DOC_Facilities.xlsx
+++ b/data/AR_DOC_Facilities.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
-  <si>
-    <t>Facility Name</t>
-  </si>
-  <si>
-    <t>Mailing Address</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Address</t>
   </si>
   <si>
     <t>Described Location</t>
@@ -34,7 +34,7 @@
     <t>West of Pine Bluff, off West 7th St. (Pine Bluff Complex) in Jefferson County</t>
   </si>
   <si>
-    <t>Benny Magness Unit (formerly North Central Unit)</t>
+    <t xml:space="preserve">Benny Magness Unit </t>
   </si>
   <si>
     <t>10 Prison Circle, Calico Rock, AR 72519</t>
@@ -94,7 +94,7 @@
     <t>10 miles south of Little Rock, off Highway 365 in Wrightsville (Pulaski Co.)</t>
   </si>
   <si>
-    <t>Larry B. Norris Unit (formerly Maximum Security Unit)</t>
+    <t>Larry B. Norris Unit ]</t>
   </si>
   <si>
     <t>2501 State Farm Rd., Tucker, AR 72168-8713</t>
@@ -155,9 +155,6 @@
   </si>
   <si>
     <t>8400 Highway 386, Wrightsville, AR 72183</t>
-  </si>
-  <si>
-    <t>Total Capacity:</t>
   </si>
 </sst>
 </file>
@@ -235,11 +232,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -249,13 +249,13 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -497,245 +497,240 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="34.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>641.0</v>
       </c>
     </row>
     <row r="3" ht="34.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="7">
         <v>800.0</v>
       </c>
     </row>
     <row r="4" ht="34.5" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>325.0</v>
       </c>
     </row>
     <row r="5" ht="34.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="7">
         <v>1876.0</v>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>599.0</v>
       </c>
     </row>
     <row r="7" ht="34.5" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>1648.0</v>
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="7">
         <v>1012.0</v>
       </c>
     </row>
     <row r="9" ht="34.5" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>212.0</v>
       </c>
     </row>
     <row r="10" ht="34.5" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="7">
         <v>532.0</v>
       </c>
     </row>
     <row r="11" ht="34.5" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>1050.0</v>
       </c>
     </row>
     <row r="12" ht="34.5" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="7">
         <v>1782.0</v>
       </c>
     </row>
     <row r="13" ht="34.5" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>430.0</v>
       </c>
     </row>
     <row r="14" ht="34.5" customHeight="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="7">
         <v>562.0</v>
       </c>
     </row>
     <row r="15" ht="34.5" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>968.0</v>
       </c>
     </row>
     <row r="16" ht="34.5" customHeight="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="7">
         <v>1714.0</v>
       </c>
     </row>
     <row r="17" ht="34.5" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="7">
         <v>850.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="9">
-        <f>SUMIF(D2:D17,"&lt;&gt;N/A",D2:D17)</f>
-        <v>15001</v>
-      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
